--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run4/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run4/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,784 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8582,0.0335,0.0440,0.0770</t>
-  </si>
-  <si>
-    <t>0.0037,0.0013,0.0001,0.9983</t>
-  </si>
-  <si>
-    <t>0.9684,0.0036,0.0002,0.0307</t>
-  </si>
-  <si>
-    <t>0.4182,0.0009,0.0003,0.8573</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9969,0.0009,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.9955,0.0018,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9966,0.0017,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9796,0.0227,0.0006,0.0014</t>
-  </si>
-  <si>
-    <t>0.9958,0.0041,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.8841,0.0114,0.1104,0.0003</t>
-  </si>
-  <si>
-    <t>0.0559,0.0250,0.9257,0.0079</t>
-  </si>
-  <si>
-    <t>0.1284,0.0178,0.8951,0.0003</t>
-  </si>
-  <si>
-    <t>0.0332,0.0013,0.9754,0.0010</t>
-  </si>
-  <si>
-    <t>0.6419,0.0660,0.3106,0.0066</t>
-  </si>
-  <si>
-    <t>0.0027,0.9953,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.0047,0.9898,0.0065,0.0026</t>
-  </si>
-  <si>
-    <t>0.0185,0.9790,0.0009,0.0020</t>
-  </si>
-  <si>
-    <t>0.0417,0.9563,0.0025,0.0041</t>
-  </si>
-  <si>
-    <t>0.0020,0.9954,0.0018,0.0012</t>
-  </si>
-  <si>
-    <t>0.6348,0.0034,0.5633,0.0010</t>
-  </si>
-  <si>
-    <t>0.3188,0.0020,0.8170,0.0005</t>
-  </si>
-  <si>
-    <t>0.0012,0.0020,0.9967,0.0007</t>
-  </si>
-  <si>
-    <t>0.0061,0.0023,0.9924,0.0002</t>
-  </si>
-  <si>
-    <t>0.0340,0.0008,0.9826,0.0005</t>
-  </si>
-  <si>
-    <t>0.0546,0.0003,0.9752,0.0003</t>
-  </si>
-  <si>
-    <t>0.0119,0.0010,0.9884,0.0013</t>
-  </si>
-  <si>
-    <t>0.2190,0.8679,0.0010,0.0012</t>
-  </si>
-  <si>
-    <t>0.5583,0.1469,0.1982,0.0014</t>
-  </si>
-  <si>
-    <t>0.0010,0.0096,0.9967,0.0022</t>
-  </si>
-  <si>
-    <t>0.0169,0.9658,0.0686,0.0009</t>
-  </si>
-  <si>
-    <t>0.9660,0.0250,0.0040,0.0042</t>
-  </si>
-  <si>
-    <t>0.9803,0.0090,0.0062,0.0013</t>
-  </si>
-  <si>
-    <t>0.7663,0.2455,0.0160,0.0026</t>
-  </si>
-  <si>
-    <t>0.0042,0.9826,0.2731,0.0011</t>
-  </si>
-  <si>
-    <t>0.0448,0.1427,0.7652,0.0022</t>
-  </si>
-  <si>
-    <t>0.2016,0.0304,0.8383,0.0059</t>
-  </si>
-  <si>
-    <t>0.0532,0.0043,0.9643,0.0008</t>
-  </si>
-  <si>
-    <t>0.1169,0.0032,0.8932,0.0106</t>
-  </si>
-  <si>
-    <t>0.0188,0.1454,0.9629,0.0008</t>
-  </si>
-  <si>
-    <t>0.0022,0.9930,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.0029,0.0043,0.9940,0.0008</t>
-  </si>
-  <si>
-    <t>0.3344,0.2101,0.0661,0.6103</t>
-  </si>
-  <si>
-    <t>0.0008,0.9836,0.0036,0.0450</t>
-  </si>
-  <si>
-    <t>0.0028,0.9886,0.0194,0.0019</t>
-  </si>
-  <si>
-    <t>0.0002,0.9964,0.0735,0.0016</t>
-  </si>
-  <si>
-    <t>0.0070,0.0216,0.9812,0.0046</t>
-  </si>
-  <si>
-    <t>0.0006,0.1939,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0123,0.0010,0.9871,0.0005</t>
-  </si>
-  <si>
-    <t>0.0114,0.0008,0.9918,0.0005</t>
-  </si>
-  <si>
-    <t>0.0097,0.0226,0.9809,0.0014</t>
-  </si>
-  <si>
-    <t>0.0255,0.0545,0.9756,0.0004</t>
-  </si>
-  <si>
-    <t>0.9375,0.0863,0.0031,0.0009</t>
-  </si>
-  <si>
-    <t>0.9849,0.0051,0.0060,0.0030</t>
-  </si>
-  <si>
-    <t>0.8576,0.2044,0.0027,0.0009</t>
-  </si>
-  <si>
-    <t>0.0015,0.0361,0.9981,0.0004</t>
-  </si>
-  <si>
-    <t>0.9968,0.0008,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9915,0.0099,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9782,0.0200,0.0024,0.0012</t>
-  </si>
-  <si>
-    <t>0.0011,0.8464,0.9814,0.0004</t>
-  </si>
-  <si>
-    <t>0.0056,0.0094,0.9929,0.0005</t>
-  </si>
-  <si>
-    <t>0.0093,0.0020,0.9924,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.9720,0.9818,0.0004</t>
-  </si>
-  <si>
-    <t>0.0022,0.0006,0.9968,0.0005</t>
-  </si>
-  <si>
-    <t>0.0058,0.9834,0.0278,0.0052</t>
-  </si>
-  <si>
-    <t>0.0043,0.9917,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.9945,0.0006,0.0051,0.0003</t>
-  </si>
-  <si>
-    <t>0.3232,0.0397,0.7101,0.0186</t>
-  </si>
-  <si>
-    <t>0.0065,0.0133,0.9921,0.0007</t>
-  </si>
-  <si>
-    <t>0.0055,0.8822,0.8601,0.0017</t>
-  </si>
-  <si>
-    <t>0.0037,0.2876,0.9703,0.0008</t>
-  </si>
-  <si>
-    <t>0.0007,0.9959,0.1613,0.0004</t>
-  </si>
-  <si>
-    <t>0.0014,0.9562,0.8544,0.0005</t>
-  </si>
-  <si>
-    <t>0.0095,0.0009,0.0426,0.9775</t>
-  </si>
-  <si>
-    <t>0.0038,0.0015,0.0009,0.9963</t>
-  </si>
-  <si>
-    <t>0.0028,0.0015,0.0002,0.9984</t>
-  </si>
-  <si>
-    <t>0.0063,0.0026,0.0041,0.9937</t>
-  </si>
-  <si>
-    <t>0.0090,0.0008,0.0029,0.9934</t>
-  </si>
-  <si>
-    <t>0.0063,0.0010,0.0025,0.9940</t>
-  </si>
-  <si>
-    <t>0.0008,0.9860,0.7628,0.0002</t>
-  </si>
-  <si>
-    <t>0.0046,0.6520,0.9623,0.0026</t>
-  </si>
-  <si>
-    <t>0.0060,0.5568,0.9028,0.0004</t>
-  </si>
-  <si>
-    <t>0.0029,0.1898,0.9845,0.0023</t>
-  </si>
-  <si>
-    <t>0.0002,0.9710,0.9879,0.0001</t>
-  </si>
-  <si>
-    <t>0.0430,0.5113,0.7843,0.0012</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9936,0.0099,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9949,0.0076,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0013,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9969,0.0012,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9978,0.0013,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9933,0.0065,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9960,0.0031,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9975,0.0007,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9987,0.0008,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0000,0.0001</t>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9676,0.0215,0.0073,0.0050</t>
+  </si>
+  <si>
+    <t>0.0312,0.0014,0.0002,0.9908</t>
+  </si>
+  <si>
+    <t>0.8934,0.0049,0.0016,0.1336</t>
+  </si>
+  <si>
+    <t>0.5777,0.0079,0.0009,0.6993</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9954,0.0031,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9931,0.0023,0.0028,0.0006</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9964,0.0030,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9908,0.0092,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9980,0.0008,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.7797,0.0200,0.2377,0.0013</t>
+  </si>
+  <si>
+    <t>0.1461,0.0030,0.9508,0.0002</t>
+  </si>
+  <si>
+    <t>0.1794,0.0085,0.8804,0.0000</t>
+  </si>
+  <si>
+    <t>0.0231,0.0010,0.9826,0.0010</t>
+  </si>
+  <si>
+    <t>0.8332,0.0180,0.2519,0.0046</t>
+  </si>
+  <si>
+    <t>0.0046,0.9952,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0146,0.9852,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.0909,0.9351,0.0013,0.0025</t>
+  </si>
+  <si>
+    <t>0.0583,0.9217,0.0233,0.0079</t>
+  </si>
+  <si>
+    <t>0.0023,0.9947,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.5185,0.0030,0.6621,0.0017</t>
+  </si>
+  <si>
+    <t>0.6980,0.0310,0.3986,0.0043</t>
+  </si>
+  <si>
+    <t>0.0012,0.0011,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.2658,0.0040,0.8521,0.0013</t>
+  </si>
+  <si>
+    <t>0.1276,0.0019,0.9130,0.0088</t>
+  </si>
+  <si>
+    <t>0.3012,0.0050,0.8317,0.0031</t>
+  </si>
+  <si>
+    <t>0.0209,0.0008,0.9790,0.0016</t>
+  </si>
+  <si>
+    <t>0.4805,0.7101,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.8406,0.1071,0.0499,0.0034</t>
+  </si>
+  <si>
+    <t>0.0005,0.0258,0.9977,0.0041</t>
+  </si>
+  <si>
+    <t>0.0180,0.9675,0.0348,0.0010</t>
+  </si>
+  <si>
+    <t>0.9476,0.0333,0.0122,0.0029</t>
+  </si>
+  <si>
+    <t>0.9678,0.0225,0.0073,0.0015</t>
+  </si>
+  <si>
+    <t>0.4618,0.5690,0.0297,0.0026</t>
+  </si>
+  <si>
+    <t>0.0067,0.9895,0.0362,0.0014</t>
+  </si>
+  <si>
+    <t>0.0126,0.8139,0.2132,0.0060</t>
+  </si>
+  <si>
+    <t>0.2471,0.0016,0.8370,0.0013</t>
+  </si>
+  <si>
+    <t>0.0232,0.0256,0.9783,0.0006</t>
+  </si>
+  <si>
+    <t>0.0119,0.0019,0.9810,0.0042</t>
+  </si>
+  <si>
+    <t>0.0064,0.0761,0.9823,0.0021</t>
+  </si>
+  <si>
+    <t>0.0039,0.9918,0.0039,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.0038,0.9950,0.0010</t>
+  </si>
+  <si>
+    <t>0.1891,0.5741,0.0998,0.5250</t>
+  </si>
+  <si>
+    <t>0.0048,0.9356,0.0882,0.0225</t>
+  </si>
+  <si>
+    <t>0.0022,0.9886,0.0085,0.0077</t>
+  </si>
+  <si>
+    <t>0.0013,0.9961,0.0033,0.0010</t>
+  </si>
+  <si>
+    <t>0.0033,0.0033,0.9947,0.0005</t>
+  </si>
+  <si>
+    <t>0.0032,0.3907,0.9902,0.0002</t>
+  </si>
+  <si>
+    <t>0.0109,0.0006,0.9925,0.0002</t>
+  </si>
+  <si>
+    <t>0.0036,0.0007,0.9969,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.0024,0.9952,0.0009</t>
+  </si>
+  <si>
+    <t>0.0109,0.1529,0.9727,0.0008</t>
+  </si>
+  <si>
+    <t>0.9123,0.1241,0.0062,0.0024</t>
+  </si>
+  <si>
+    <t>0.9799,0.0013,0.0142,0.0037</t>
+  </si>
+  <si>
+    <t>0.7631,0.1700,0.0402,0.0015</t>
+  </si>
+  <si>
+    <t>0.0040,0.0367,0.9947,0.0017</t>
+  </si>
+  <si>
+    <t>0.9954,0.0009,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9956,0.0045,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9486,0.1106,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9797,0.9687,0.0001</t>
+  </si>
+  <si>
+    <t>0.0066,0.0590,0.9916,0.0003</t>
+  </si>
+  <si>
+    <t>0.0092,0.0083,0.9865,0.0013</t>
+  </si>
+  <si>
+    <t>0.0006,0.9728,0.9788,0.0005</t>
+  </si>
+  <si>
+    <t>0.0007,0.0008,0.9975,0.0016</t>
+  </si>
+  <si>
+    <t>0.0166,0.9670,0.0327,0.0008</t>
+  </si>
+  <si>
+    <t>0.0015,0.9955,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9768,0.0059,0.0170,0.0021</t>
+  </si>
+  <si>
+    <t>0.8074,0.1478,0.0202,0.0196</t>
+  </si>
+  <si>
+    <t>0.0014,0.0098,0.9978,0.0004</t>
+  </si>
+  <si>
+    <t>0.0067,0.8632,0.8267,0.0019</t>
+  </si>
+  <si>
+    <t>0.0017,0.8255,0.9615,0.0006</t>
+  </si>
+  <si>
+    <t>0.0017,0.9944,0.1130,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9920,0.9485,0.0002</t>
+  </si>
+  <si>
+    <t>0.0251,0.0044,0.0268,0.9711</t>
+  </si>
+  <si>
+    <t>0.0046,0.0163,0.0007,0.9961</t>
+  </si>
+  <si>
+    <t>0.0056,0.0009,0.0002,0.9976</t>
+  </si>
+  <si>
+    <t>0.0028,0.0024,0.0012,0.9971</t>
+  </si>
+  <si>
+    <t>0.0043,0.0059,0.0200,0.9889</t>
+  </si>
+  <si>
+    <t>0.0056,0.0017,0.0016,0.9958</t>
+  </si>
+  <si>
+    <t>0.0002,0.9836,0.9684,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.9606,0.9741,0.0004</t>
+  </si>
+  <si>
+    <t>0.0085,0.4594,0.9046,0.0011</t>
+  </si>
+  <si>
+    <t>0.0036,0.1458,0.9851,0.0010</t>
+  </si>
+  <si>
+    <t>0.0003,0.9926,0.8974,0.0000</t>
+  </si>
+  <si>
+    <t>0.0172,0.8410,0.4840,0.0015</t>
+  </si>
+  <si>
+    <t>0.9981,0.0007,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9971,0.0041,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9856,0.0201,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9981,0.0009,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9864,0.0103,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9979,0.0010,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9875,0.0080,0.0004,0.0024</t>
+  </si>
+  <si>
+    <t>0.9979,0.0010,0.0002,0.0003</t>
   </si>
   <si>
     <t>0.9995,0.0001,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9986,0.0008,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9972,0.0010,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9970,0.0009,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.0042,0.0010,0.9927,0.0027</t>
-  </si>
-  <si>
-    <t>0.0499,0.0056,0.9637,0.0022</t>
-  </si>
-  <si>
-    <t>0.9930,0.0003,0.0052,0.0002</t>
-  </si>
-  <si>
-    <t>0.0100,0.0006,0.9897,0.0025</t>
-  </si>
-  <si>
-    <t>0.0105,0.9858,0.0005,0.0012</t>
-  </si>
-  <si>
-    <t>0.0009,0.9979,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.0073,0.9861,0.0020,0.0019</t>
-  </si>
-  <si>
-    <t>0.0199,0.9687,0.0068,0.0075</t>
-  </si>
-  <si>
-    <t>0.0015,0.9975,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.0034,0.9913,0.0028,0.0011</t>
-  </si>
-  <si>
-    <t>0.8236,0.3182,0.0014,0.0006</t>
-  </si>
-  <si>
-    <t>0.7883,0.1464,0.0378,0.0088</t>
-  </si>
-  <si>
-    <t>0.6276,0.0097,0.5068,0.0014</t>
-  </si>
-  <si>
-    <t>0.5555,0.0134,0.4649,0.0036</t>
-  </si>
-  <si>
-    <t>0.8901,0.0027,0.1633,0.0006</t>
-  </si>
-  <si>
-    <t>0.0446,0.1041,0.1262,0.7593</t>
-  </si>
-  <si>
-    <t>0.0021,0.9903,0.0120,0.0016</t>
-  </si>
-  <si>
-    <t>0.0021,0.9864,0.0054,0.0083</t>
-  </si>
-  <si>
-    <t>0.0007,0.9947,0.0032,0.0136</t>
-  </si>
-  <si>
-    <t>0.0020,0.9754,0.2181,0.0019</t>
-  </si>
-  <si>
-    <t>0.0030,0.9967,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.5429,0.5410,0.0256,0.0021</t>
-  </si>
-  <si>
-    <t>0.5164,0.4889,0.0284,0.0011</t>
-  </si>
-  <si>
-    <t>0.9955,0.0018,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.9976,0.0012,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9981,0.0005,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9941,0.0013,0.0010,0.0021</t>
-  </si>
-  <si>
-    <t>0.9980,0.0007,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9964,0.0009,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9916,0.0032,0.0007,0.0032</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.0017,0.0204,0.9951,0.0002</t>
-  </si>
-  <si>
-    <t>0.0117,0.1531,0.9072,0.0008</t>
-  </si>
-  <si>
-    <t>0.0141,0.0098,0.9769,0.0009</t>
-  </si>
-  <si>
-    <t>0.0338,0.0509,0.9624,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0002,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.8799,0.0010,0.1216,0.0089</t>
-  </si>
-  <si>
-    <t>0.3972,0.0026,0.8441,0.0004</t>
-  </si>
-  <si>
-    <t>0.9873,0.0068,0.0016,0.0016</t>
-  </si>
-  <si>
-    <t>0.2386,0.0018,0.0019,0.8936</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.0011,0.9996</t>
-  </si>
-  <si>
-    <t>0.0010,0.0010,0.0008,0.9983</t>
-  </si>
-  <si>
-    <t>0.0022,0.0023,0.0029,0.9969</t>
-  </si>
-  <si>
-    <t>0.0011,0.3155,0.9708,0.0013</t>
-  </si>
-  <si>
-    <t>0.9981,0.0004,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.6509,0.4606,0.0022,0.0062</t>
-  </si>
-  <si>
-    <t>0.9978,0.0006,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.8644,0.2033,0.0066,0.0031</t>
-  </si>
-  <si>
-    <t>0.9907,0.0023,0.0058,0.0011</t>
-  </si>
-  <si>
-    <t>0.6461,0.0054,0.0068,0.5618</t>
-  </si>
-  <si>
-    <t>0.9960,0.0005,0.0001,0.0036</t>
-  </si>
-  <si>
-    <t>0.0006,0.0078,0.9931,0.0210</t>
-  </si>
-  <si>
-    <t>0.7776,0.0007,0.0182,0.1521</t>
-  </si>
-  <si>
-    <t>0.9570,0.0042,0.0024,0.0663</t>
-  </si>
-  <si>
-    <t>0.3608,0.7130,0.0047,0.0034</t>
-  </si>
-  <si>
-    <t>0.9657,0.0187,0.0081,0.0050</t>
-  </si>
-  <si>
-    <t>0.9787,0.0185,0.0023,0.0011</t>
-  </si>
-  <si>
-    <t>0.0622,0.9209,0.0144,0.0046</t>
-  </si>
-  <si>
-    <t>0.9894,0.0051,0.0026,0.0005</t>
-  </si>
-  <si>
-    <t>0.9862,0.0074,0.0022,0.0014</t>
-  </si>
-  <si>
-    <t>0.9947,0.0019,0.0006,0.0013</t>
-  </si>
-  <si>
-    <t>0.9970,0.0008,0.0003,0.0013</t>
-  </si>
-  <si>
-    <t>0.9972,0.0014,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9980,0.0004,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9949,0.0011,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.9929,0.0069,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9969,0.0007,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9976,0.0007,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.7678,0.2918,0.0069,0.0018</t>
-  </si>
-  <si>
-    <t>0.9489,0.0898,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.3595,0.7856,0.0005,0.0012</t>
-  </si>
-  <si>
-    <t>0.0058,0.2363,0.9911,0.0013</t>
-  </si>
-  <si>
-    <t>0.9862,0.0199,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9770,0.0123,0.0068,0.0019</t>
-  </si>
-  <si>
-    <t>0.9978,0.0009,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9803,0.0255,0.0006,0.0011</t>
-  </si>
-  <si>
-    <t>0.0004,0.0699,0.9989,0.0013</t>
-  </si>
-  <si>
-    <t>0.9041,0.0710,0.0217,0.0014</t>
-  </si>
-  <si>
-    <t>0.0003,0.0006,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.0060,0.9948,0.0012</t>
-  </si>
-  <si>
-    <t>0.0501,0.0023,0.9730,0.0009</t>
-  </si>
-  <si>
-    <t>0.0069,0.0396,0.9879,0.0004</t>
-  </si>
-  <si>
-    <t>0.0020,0.0123,0.9964,0.0003</t>
-  </si>
-  <si>
-    <t>0.0015,0.0008,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.0073,0.9957,0.0012</t>
-  </si>
-  <si>
-    <t>0.2891,0.0024,0.8438,0.0018</t>
-  </si>
-  <si>
-    <t>0.3071,0.0232,0.7634,0.0068</t>
-  </si>
-  <si>
-    <t>0.3474,0.0700,0.5982,0.0523</t>
-  </si>
-  <si>
-    <t>0.5165,0.0456,0.3422,0.0004</t>
-  </si>
-  <si>
-    <t>0.2188,0.6137,0.0584,0.0004</t>
-  </si>
-  <si>
-    <t>0.5919,0.0183,0.4813,0.0031</t>
-  </si>
-  <si>
-    <t>0.8929,0.0077,0.1409,0.0035</t>
-  </si>
-  <si>
-    <t>0.0399,0.0062,0.9505,0.0035</t>
-  </si>
-  <si>
-    <t>0.8974,0.2349,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.5459,0.6614,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9851,0.0164,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.8065,0.3421,0.0013,0.0010</t>
-  </si>
-  <si>
-    <t>0.8596,0.3318,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.8898,0.0212,0.0944,0.0015</t>
-  </si>
-  <si>
-    <t>0.9387,0.0074,0.0596,0.0031</t>
-  </si>
-  <si>
-    <t>0.9579,0.0027,0.0208,0.0090</t>
-  </si>
-  <si>
-    <t>0.3611,0.0095,0.7084,0.0083</t>
-  </si>
-  <si>
-    <t>0.8777,0.0052,0.1328,0.0105</t>
-  </si>
-  <si>
-    <t>0.0081,0.0056,0.9832,0.0107</t>
-  </si>
-  <si>
-    <t>0.0033,0.0147,0.9916,0.0019</t>
-  </si>
-  <si>
-    <t>0.0028,0.0115,0.9931,0.0019</t>
-  </si>
-  <si>
-    <t>0.3899,0.0012,0.8250,0.0003</t>
-  </si>
-  <si>
-    <t>0.0041,0.0219,0.9748,0.0039</t>
-  </si>
-  <si>
-    <t>0.9904,0.0065,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9968,0.0026,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9340,0.1161,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9959,0.0028,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9939,0.0043,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.9851,0.0242,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9932,0.0028,0.0012,0.0015</t>
+    <t>0.9982,0.0009,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9947,0.0020,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.9974,0.0026,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9969,0.0007,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.0021,0.0003,0.9930,0.0077</t>
+  </si>
+  <si>
+    <t>0.0427,0.0036,0.9597,0.0043</t>
+  </si>
+  <si>
+    <t>0.9891,0.0005,0.0077,0.0004</t>
+  </si>
+  <si>
+    <t>0.0243,0.0035,0.9887,0.0003</t>
+  </si>
+  <si>
+    <t>0.0019,0.9965,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.9987,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.0230,0.9736,0.0026,0.0019</t>
+  </si>
+  <si>
+    <t>0.0078,0.9854,0.0067,0.0040</t>
+  </si>
+  <si>
+    <t>0.0069,0.9889,0.0021,0.0009</t>
+  </si>
+  <si>
+    <t>0.0033,0.9926,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.8088,0.3082,0.0022,0.0017</t>
+  </si>
+  <si>
+    <t>0.9219,0.0263,0.0396,0.0036</t>
+  </si>
+  <si>
+    <t>0.1763,0.0077,0.8889,0.0028</t>
+  </si>
+  <si>
+    <t>0.6651,0.0108,0.3050,0.0253</t>
+  </si>
+  <si>
+    <t>0.5003,0.0019,0.7558,0.0003</t>
+  </si>
+  <si>
+    <t>0.0727,0.0203,0.2686,0.8013</t>
+  </si>
+  <si>
+    <t>0.0010,0.9949,0.0118,0.0015</t>
+  </si>
+  <si>
+    <t>0.0011,0.9954,0.0029,0.0010</t>
+  </si>
+  <si>
+    <t>0.0020,0.9869,0.0369,0.0358</t>
+  </si>
+  <si>
+    <t>0.0021,0.9699,0.3689,0.0006</t>
+  </si>
+  <si>
+    <t>0.0011,0.9982,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.3039,0.7864,0.0088,0.0005</t>
+  </si>
+  <si>
+    <t>0.6831,0.3853,0.0106,0.0028</t>
+  </si>
+  <si>
+    <t>0.9957,0.0025,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9976,0.0007,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9936,0.0008,0.0040,0.0010</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0010,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9951,0.0009,0.0012,0.0016</t>
+  </si>
+  <si>
+    <t>0.9974,0.0005,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.0019,0.1290,0.9869,0.0001</t>
+  </si>
+  <si>
+    <t>0.0081,0.7033,0.7636,0.0004</t>
+  </si>
+  <si>
+    <t>0.0033,0.0090,0.9924,0.0011</t>
+  </si>
+  <si>
+    <t>0.0421,0.0992,0.8859,0.0004</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.7795,0.0275,0.1916,0.0064</t>
+  </si>
+  <si>
+    <t>0.3186,0.0011,0.8858,0.0006</t>
+  </si>
+  <si>
+    <t>0.9219,0.0264,0.0331,0.0107</t>
+  </si>
+  <si>
+    <t>0.1167,0.0006,0.0001,0.9709</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.0036,0.9989</t>
+  </si>
+  <si>
+    <t>0.0120,0.0055,0.0033,0.9865</t>
+  </si>
+  <si>
+    <t>0.0029,0.0020,0.0048,0.9962</t>
+  </si>
+  <si>
+    <t>0.0012,0.4424,0.9428,0.0017</t>
+  </si>
+  <si>
+    <t>0.9935,0.0033,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.1227,0.9053,0.0037,0.0050</t>
+  </si>
+  <si>
+    <t>0.9947,0.0013,0.0026,0.0006</t>
+  </si>
+  <si>
+    <t>0.9293,0.0794,0.0102,0.0083</t>
+  </si>
+  <si>
+    <t>0.9935,0.0017,0.0013,0.0015</t>
+  </si>
+  <si>
+    <t>0.2871,0.0153,0.0018,0.8625</t>
+  </si>
+  <si>
+    <t>0.9951,0.0008,0.0003,0.0032</t>
+  </si>
+  <si>
+    <t>0.0002,0.0077,0.9973,0.0228</t>
+  </si>
+  <si>
+    <t>0.9907,0.0002,0.0003,0.0091</t>
+  </si>
+  <si>
+    <t>0.8970,0.0024,0.0016,0.2235</t>
+  </si>
+  <si>
+    <t>0.7781,0.1811,0.0229,0.0042</t>
+  </si>
+  <si>
+    <t>0.9799,0.0142,0.0017,0.0030</t>
+  </si>
+  <si>
+    <t>0.9877,0.0089,0.0015,0.0007</t>
+  </si>
+  <si>
+    <t>0.3216,0.2612,0.2386,0.0340</t>
+  </si>
+  <si>
+    <t>0.9933,0.0070,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9350,0.0510,0.0117,0.0008</t>
+  </si>
+  <si>
+    <t>0.9965,0.0012,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9985,0.0005,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9979,0.0007,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9969,0.0006,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9932,0.0022,0.0017,0.0011</t>
+  </si>
+  <si>
+    <t>0.9903,0.0105,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9946,0.0016,0.0016,0.0008</t>
+  </si>
+  <si>
+    <t>0.9979,0.0006,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.7963,0.2504,0.0079,0.0029</t>
+  </si>
+  <si>
+    <t>0.6272,0.5574,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.1371,0.9170,0.0034,0.0012</t>
+  </si>
+  <si>
+    <t>0.0279,0.0994,0.9776,0.0022</t>
+  </si>
+  <si>
+    <t>0.9761,0.0369,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9858,0.0063,0.0048,0.0024</t>
+  </si>
+  <si>
+    <t>0.9919,0.0046,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.9872,0.0081,0.0004,0.0028</t>
+  </si>
+  <si>
+    <t>0.0004,0.0209,0.9992,0.0007</t>
+  </si>
+  <si>
+    <t>0.9648,0.0293,0.0058,0.0011</t>
+  </si>
+  <si>
+    <t>0.0001,0.0017,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.0090,0.9964,0.0012</t>
+  </si>
+  <si>
+    <t>0.0044,0.0017,0.9945,0.0025</t>
+  </si>
+  <si>
+    <t>0.0235,0.0706,0.9635,0.0009</t>
+  </si>
+  <si>
+    <t>0.0008,0.0012,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.0073,0.0007,0.9952,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.0019,0.9937,0.0110</t>
+  </si>
+  <si>
+    <t>0.0341,0.0037,0.9624,0.0069</t>
+  </si>
+  <si>
+    <t>0.0811,0.0228,0.9239,0.0029</t>
+  </si>
+  <si>
+    <t>0.0215,0.0130,0.9699,0.0018</t>
+  </si>
+  <si>
+    <t>0.8181,0.0182,0.1600,0.0005</t>
+  </si>
+  <si>
+    <t>0.1180,0.0233,0.8629,0.0009</t>
+  </si>
+  <si>
+    <t>0.2166,0.0309,0.8029,0.0016</t>
+  </si>
+  <si>
+    <t>0.6997,0.0216,0.3639,0.0078</t>
+  </si>
+  <si>
+    <t>0.1565,0.0103,0.8617,0.0128</t>
+  </si>
+  <si>
+    <t>0.1094,0.9542,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.5030,0.6288,0.0052,0.0013</t>
+  </si>
+  <si>
+    <t>0.9669,0.0663,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.6018,0.5894,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9590,0.0784,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.8231,0.0389,0.1173,0.0057</t>
+  </si>
+  <si>
+    <t>0.9645,0.0007,0.0484,0.0009</t>
+  </si>
+  <si>
+    <t>0.9486,0.0014,0.0372,0.0070</t>
+  </si>
+  <si>
+    <t>0.7978,0.0167,0.2895,0.0008</t>
+  </si>
+  <si>
+    <t>0.8914,0.0075,0.1014,0.0052</t>
+  </si>
+  <si>
+    <t>0.0032,0.0029,0.9913,0.0131</t>
+  </si>
+  <si>
+    <t>0.0017,0.0042,0.9942,0.0018</t>
+  </si>
+  <si>
+    <t>0.0266,0.0188,0.9734,0.0009</t>
+  </si>
+  <si>
+    <t>0.5754,0.0029,0.5720,0.0013</t>
+  </si>
+  <si>
+    <t>0.0057,0.0490,0.9782,0.0006</t>
+  </si>
+  <si>
+    <t>0.9951,0.0026,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9959,0.0025,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9832,0.0187,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9752,0.0216,0.0022,0.0002</t>
+  </si>
+  <si>
+    <t>0.9871,0.0116,0.0012,0.0012</t>
+  </si>
+  <si>
+    <t>0.9953,0.0047,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9904,0.0025,0.0055,0.0007</t>
   </si>
   <si>
     <t>0.9975,0.0009,0.0003,0.0004</t>
   </si>
   <si>
-    <t>0.0203,0.0148,0.9847,0.0025</t>
-  </si>
-  <si>
-    <t>0.0641,0.2948,0.5938,0.0249</t>
-  </si>
-  <si>
-    <t>0.6705,0.0045,0.4275,0.0057</t>
-  </si>
-  <si>
-    <t>0.0060,0.0076,0.9914,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.0010,0.9986,0.0008</t>
-  </si>
-  <si>
-    <t>0.0110,0.0250,0.9865,0.0005</t>
-  </si>
-  <si>
-    <t>0.0016,0.0038,0.9980,0.0002</t>
-  </si>
-  <si>
-    <t>0.0093,0.0027,0.9839,0.0037</t>
-  </si>
-  <si>
-    <t>0.0070,0.0039,0.9946,0.0002</t>
-  </si>
-  <si>
-    <t>0.0116,0.0054,0.9848,0.0005</t>
-  </si>
-  <si>
-    <t>0.0123,0.0047,0.9799,0.0017</t>
-  </si>
-  <si>
-    <t>0.7180,0.0062,0.3884,0.0049</t>
-  </si>
-  <si>
-    <t>0.8548,0.0024,0.3013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9623,0.0049,0.0311,0.0012</t>
-  </si>
-  <si>
-    <t>0.9739,0.0350,0.0017,0.0014</t>
-  </si>
-  <si>
-    <t>0.9982,0.0020,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9954,0.0044,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9976,0.0012,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9922,0.0076,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9875,0.0092,0.0011,0.0011</t>
-  </si>
-  <si>
-    <t>0.9979,0.0006,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.0116,0.0199,0.9610,0.0024</t>
-  </si>
-  <si>
-    <t>0.0007,0.4139,0.9946,0.0007</t>
-  </si>
-  <si>
-    <t>0.0441,0.0051,0.9796,0.0001</t>
-  </si>
-  <si>
-    <t>0.0393,0.0186,0.9367,0.0023</t>
-  </si>
-  <si>
-    <t>0.0147,0.0011,0.9891,0.0004</t>
-  </si>
-  <si>
-    <t>0.0538,0.0727,0.8523,0.1932</t>
-  </si>
-  <si>
-    <t>0.0041,0.1163,0.9793,0.0088</t>
-  </si>
-  <si>
-    <t>0.0222,0.0012,0.9726,0.0051</t>
-  </si>
-  <si>
-    <t>0.9520,0.0002,0.0004,0.0964</t>
-  </si>
-  <si>
-    <t>0.3865,0.0071,0.0004,0.8597</t>
-  </si>
-  <si>
-    <t>0.0588,0.0009,0.0011,0.9793</t>
-  </si>
-  <si>
-    <t>0.0213,0.0003,0.0010,0.9913</t>
-  </si>
-  <si>
-    <t>0.0086,0.0003,0.0003,0.9949</t>
-  </si>
-  <si>
-    <t>0.9695,0.0058,0.0010,0.0307</t>
+    <t>0.0118,0.0163,0.9931,0.0004</t>
+  </si>
+  <si>
+    <t>0.0462,0.0820,0.8775,0.0030</t>
+  </si>
+  <si>
+    <t>0.9098,0.0010,0.1280,0.0013</t>
+  </si>
+  <si>
+    <t>0.0033,0.0076,0.9967,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0041,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.0052,0.0354,0.9848,0.0029</t>
+  </si>
+  <si>
+    <t>0.0023,0.0064,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.0036,0.0128,0.9907,0.0035</t>
+  </si>
+  <si>
+    <t>0.0123,0.0006,0.9926,0.0002</t>
+  </si>
+  <si>
+    <t>0.0067,0.0254,0.9741,0.0013</t>
+  </si>
+  <si>
+    <t>0.0375,0.0296,0.9281,0.0217</t>
+  </si>
+  <si>
+    <t>0.8136,0.0101,0.1819,0.0394</t>
+  </si>
+  <si>
+    <t>0.9313,0.0024,0.1261,0.0006</t>
+  </si>
+  <si>
+    <t>0.9599,0.0044,0.0238,0.0058</t>
+  </si>
+  <si>
+    <t>0.9895,0.0104,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9959,0.0049,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9937,0.0036,0.0017,0.0007</t>
+  </si>
+  <si>
+    <t>0.9922,0.0054,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9976,0.0006,0.0000,0.0013</t>
+  </si>
+  <si>
+    <t>0.9902,0.0140,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9795,0.0272,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9931,0.0046,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.0225,0.0083,0.9593,0.0011</t>
+  </si>
+  <si>
+    <t>0.0014,0.0961,0.9949,0.0007</t>
+  </si>
+  <si>
+    <t>0.0831,0.0039,0.9542,0.0003</t>
+  </si>
+  <si>
+    <t>0.0277,0.0968,0.8505,0.0061</t>
+  </si>
+  <si>
+    <t>0.0082,0.0006,0.9947,0.0001</t>
+  </si>
+  <si>
+    <t>0.2187,0.0226,0.7623,0.0316</t>
+  </si>
+  <si>
+    <t>0.0139,0.0053,0.9762,0.0140</t>
+  </si>
+  <si>
+    <t>0.0132,0.0009,0.9739,0.0067</t>
+  </si>
+  <si>
+    <t>0.9074,0.0002,0.0003,0.2461</t>
+  </si>
+  <si>
+    <t>0.2265,0.0169,0.0008,0.9286</t>
+  </si>
+  <si>
+    <t>0.1735,0.0004,0.0003,0.9590</t>
+  </si>
+  <si>
+    <t>0.0021,0.0001,0.0005,0.9988</t>
+  </si>
+  <si>
+    <t>0.0213,0.0001,0.0001,0.9929</t>
+  </si>
+  <si>
+    <t>0.9889,0.0017,0.0007,0.0068</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1985,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1999,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +2010,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2069,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2083,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2097,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2125,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2139,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2153,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2167,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2181,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2195,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2209,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2223,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2237,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2251,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2265,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2276,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2290,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2307,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2321,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2335,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2349,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2363,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2377,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2391,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2419,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2433,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2447,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2458,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2486,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2503,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2517,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2531,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2545,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2559,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2584,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2601,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2615,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2629,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2643,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2657,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2671,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2699,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2713,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2741,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2755,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2783,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2797,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2811,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2825,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2839,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2853,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2867,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2881,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2895,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2923,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2934,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2951,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2965,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2976,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2993,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3007,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3021,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3035,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3049,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3063,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3077,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3091,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3105,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3119,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3130,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3147,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3161,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3172,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3329,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3343,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3371,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3385,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3399,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3413,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3427,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3441,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3455,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3483,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3497,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3511,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3525,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3539,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3553,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3567,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3581,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3595,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3606,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3623,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3637,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3651,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3665,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3679,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3693,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3707,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3721,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3763,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3777,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3791,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3805,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3847,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3858,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3875,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3889,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3903,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3917,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3931,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3945,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3959,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3973,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3987,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +4001,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4015,7 @@
         <v>261</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4040,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4071,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4085,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4099,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4127,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4141,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4155,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4166,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4208,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4309,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4323,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4365,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4376,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4393,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4407,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4421,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4435,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4449,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4463,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4491,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4547,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4561,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4589,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4603,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4617,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4631,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4645,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4656,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4670,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4687,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4701,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4712,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4726,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4743,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,10 +4754,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4771,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4785,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4799,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4813,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4824,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4841,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4855,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4869,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4883,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4894,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4911,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4953,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4967,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4995,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5009,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5023,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5051,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5065,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5107,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5121,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5135,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5149,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5163,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5177,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5191,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5205,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5261,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5275,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5289,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5303,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5317,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5331,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5373,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5387,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5401,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5415,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5429,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5443,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5457,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5471,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5485,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5499,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5513,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5527,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
